--- a/export from sqliteonline.com.xlsx
+++ b/export from sqliteonline.com.xlsx
@@ -3,19 +3,40 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <sheets>
+    <sheet sheetId="1" name="Page 1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="SQL" state="visible" r:id="rId5"/>
+  </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>media_salarios</t>
+  </si>
+  <si>
+    <t>Page 1</t>
+  </si>
+  <si>
+    <t>SELECT AVG(salario) AS media_salarios FROM funcionarios;</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,8 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,4 +399,44 @@
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>3591.6666666666665</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>